--- a/app/_lib/report-template.xlsx
+++ b/app/_lib/report-template.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Expenses" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Customers" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Readings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bank" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1744,4 +1745,73 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>What for</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/app/_lib/report-template.xlsx
+++ b/app/_lib/report-template.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Customers" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Readings" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Bank" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Lubricants" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -936,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1035,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>COSTS</t>
+          <t>LUBRICANTS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr"/>
@@ -1042,7 +1043,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Fuel bought (litres)</t>
+          <t>Litres sold</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1052,7 +1053,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Fuel bought (cost)</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1062,7 +1063,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Still owed to suppliers</t>
+          <t>Cash taken</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1072,7 +1073,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Given on credit</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1086,24 +1087,86 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PROFIT</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
+          <t>COSTS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Fuel bought (litres)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Fuel bought (cost)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Lubricants bought (cost)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Still owed to suppliers</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>CLOSING STOCK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1116,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1126,6 +1189,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1162,6 +1227,16 @@
       <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Credit</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Lubricant (L)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Lubricant sales</t>
         </is>
       </c>
     </row>
@@ -1173,6 +1248,8 @@
       <c r="E2" s="7" t="n"/>
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="7" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -1182,6 +1259,8 @@
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -1191,6 +1270,8 @@
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -1200,6 +1281,8 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -1209,6 +1292,8 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1218,6 +1303,8 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1227,6 +1314,8 @@
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1236,6 +1325,8 @@
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1245,6 +1336,8 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1254,6 +1347,8 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1263,6 +1358,8 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1272,6 +1369,8 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1281,6 +1380,8 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1290,6 +1391,8 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1299,6 +1402,8 @@
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1308,6 +1413,8 @@
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1317,6 +1424,8 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1326,6 +1435,8 @@
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1335,6 +1446,8 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1344,6 +1457,8 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1353,6 +1468,8 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1362,6 +1479,8 @@
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1371,6 +1490,8 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1380,6 +1501,8 @@
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1389,6 +1512,8 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1398,6 +1523,8 @@
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1407,6 +1534,8 @@
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1416,6 +1545,8 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1425,6 +1556,8 @@
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1434,6 +1567,8 @@
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1443,6 +1578,8 @@
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1814,4 +1951,87 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Lubricant</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/app/_lib/report-template.xlsx
+++ b/app/_lib/report-template.xlsx
@@ -1971,6 +1971,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2017,6 +2018,11 @@
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Note</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Kind</t>
         </is>
       </c>
     </row>
@@ -2030,6 +2036,7 @@
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
